--- a/WorkBot/main/data/orders/Webstaurant/Webstaurant_Bakery_20260530.xlsx
+++ b/WorkBot/main/data/orders/Webstaurant/Webstaurant_Bakery_20260530.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,6 +647,90 @@
         <v>299.52</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>711SPRNKLEPK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sprinkles - Pink</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="E14" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>245S12FU14R</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cake Drum - 14"</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="E15" t="n">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>245S12FU12RCBL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cake Drum - 12" (silver)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="E16" t="n">
+        <v>244.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>711SPRNKLEGR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sprinkles - Dk Green</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="E17" t="n">
+        <v>25.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/WorkBot/main/data/orders/Webstaurant/Webstaurant_Bakery_20260530.xlsx
+++ b/WorkBot/main/data/orders/Webstaurant/Webstaurant_Bakery_20260530.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -731,6 +731,174 @@
         <v>25.62</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>433SLINERBL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sheet Pan Liner - Silicone Coated</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="E18" t="n">
+        <v>168.46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2458GCC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cake Circle - 8" (Gold)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="E19" t="n">
+        <v>77.98</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>24510GCC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cake Circle - 10" (Gold)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="E20" t="n">
+        <v>111.98</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>245CCGR1410BL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cake Board - 1/4 Sheet</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="E21" t="n">
+        <v>85.98</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>245CCGR1914</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cake Board - 1/2 Sheet</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="E22" t="n">
+        <v>79.98</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>588ESP1220</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Urnex - Cafiza</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>112.68</v>
+      </c>
+      <c r="E23" t="n">
+        <v>112.68</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>150BB4224N</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bag Paper - Baguette</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>118.99</v>
+      </c>
+      <c r="E24" t="n">
+        <v>237.98</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>433qlinerbl</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sheet Pan Liner - White</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="E25" t="n">
+        <v>140.97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
